--- a/Result/profitability/6189.xlsx
+++ b/Result/profitability/6189.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.43</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8425</v>
+        <v>0.805</v>
       </c>
       <c r="N2" t="n">
-        <v>8.19125</v>
+        <v>8.1975</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.49</v>
       </c>
       <c r="M3" t="n">
-        <v>0.74</v>
+        <v>0.72375</v>
       </c>
       <c r="N3" t="n">
-        <v>7.67625</v>
+        <v>7.953749999999999</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6837500000000001</v>
+        <v>0.645</v>
       </c>
       <c r="N4" t="n">
-        <v>7.547499999999999</v>
+        <v>7.6175</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,7 +1018,7 @@
         <v>0.12</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5337499999999999</v>
+        <v>0.7212500000000001</v>
       </c>
       <c r="N5" t="n">
         <v>7.13</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>0.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6575</v>
+        <v>0.64375</v>
       </c>
       <c r="N6" t="n">
-        <v>7.01</v>
+        <v>7.1175</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.36</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5625</v>
+        <v>0.575</v>
       </c>
       <c r="N7" t="n">
-        <v>6.86875</v>
+        <v>6.945</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.72</v>
       </c>
       <c r="M8" t="n">
-        <v>0.53875</v>
+        <v>0.54</v>
       </c>
       <c r="N8" t="n">
-        <v>6.67</v>
+        <v>6.688750000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>0.64</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5249999999999999</v>
+        <v>0.525</v>
       </c>
       <c r="N10" t="n">
         <v>6.55</v>
@@ -1775,7 +1775,7 @@
         <v>0.5649999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>6.83625</v>
+        <v>6.836250000000001</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6189</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>7574</v>
+      </c>
+      <c r="D75" t="n">
+        <v>6869</v>
+      </c>
+      <c r="E75" t="n">
+        <v>705</v>
+      </c>
+      <c r="F75" t="n">
+        <v>9.31</v>
+      </c>
+      <c r="G75" t="n">
+        <v>376</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4.97%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>375</v>
+      </c>
+      <c r="K75" t="n">
+        <v>267</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="N75" t="n">
+        <v>8.75375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.1500000000000004</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.01637554585152845</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-3.061224489795918</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
